--- a/data/trans_dic/Q25_A_R3-Edad-trans_dic.xlsx
+++ b/data/trans_dic/Q25_A_R3-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que dejo de fumar hace menos tiempo (3.374 años)</t>
+          <t>Población que dejo de fumar hace menos tiempo (3.374 años) (tasa de respuesta: 96,5%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>54,73; 100,0</t>
+          <t>53,8; 100,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>73,37; 100,0</t>
+          <t>68,56; 100,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>82,92; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>55,59; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>55,64; 100,0</t>
+          <t>56,96; 100,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>59,3; 95,04</t>
+          <t>56,4; 95,05</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,07; 89,43</t>
+          <t>51,06; 89,39</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>41,85; 100,0</t>
+          <t>38,03; 100,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>66,7; 96,11</t>
+          <t>67,01; 96,08</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>72,72; 94,88</t>
+          <t>74,04; 97,24</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>62,94; 93,25</t>
+          <t>65,66; 93,33</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>52,28; 100,0</t>
+          <t>54,9; 100,0</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>44,34; 78,64</t>
+          <t>43,56; 78,46</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>62,28; 81,76</t>
+          <t>61,05; 81,3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>35,9; 65,0</t>
+          <t>35,51; 63,3</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17,53; 74,82</t>
+          <t>15,84; 72,63</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>44,06; 68,45</t>
+          <t>46,03; 68,77</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>48,83; 71,34</t>
+          <t>49,71; 71,03</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>47,06; 71,29</t>
+          <t>45,6; 72,07</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>28,61; 65,67</t>
+          <t>29,04; 68,99</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>49,69; 68,7</t>
+          <t>50,1; 68,84</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>58,36; 73,6</t>
+          <t>58,96; 74,39</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44,76; 64,0</t>
+          <t>44,98; 64,45</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>29,47; 63,17</t>
+          <t>30,85; 63,3</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>32,35; 53,69</t>
+          <t>33,23; 54,27</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>33,29; 53,1</t>
+          <t>34,35; 53,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>35,56; 56,9</t>
+          <t>34,56; 57,2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16,03; 47,72</t>
+          <t>16,73; 47,75</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13,23; 34,68</t>
+          <t>14,38; 34,83</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19,8; 36,19</t>
+          <t>19,76; 36,68</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>21,74; 40,5</t>
+          <t>20,85; 38,92</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>23,27; 44,53</t>
+          <t>23,31; 44,99</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>27,43; 43,78</t>
+          <t>27,75; 42,92</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>28,75; 41,24</t>
+          <t>28,22; 41,31</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>29,35; 43,95</t>
+          <t>29,88; 44,52</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>23,72; 41,95</t>
+          <t>24,51; 43,29</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>22,83; 39,64</t>
+          <t>23,31; 40,25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>22,4; 36,65</t>
+          <t>22,55; 37,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17,86; 32,41</t>
+          <t>16,98; 33,06</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14,24; 94,34</t>
+          <t>14,58; 94,01</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>22,15; 44,75</t>
+          <t>20,56; 44,72</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,23; 35,11</t>
+          <t>16,56; 35,08</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,97; 31,85</t>
+          <t>14,6; 31,51</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>16,83; 31,55</t>
+          <t>16,68; 31,46</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>25,88; 38,89</t>
+          <t>25,11; 38,7</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21,89; 33,33</t>
+          <t>22,58; 33,89</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18,19; 29,43</t>
+          <t>18,47; 29,86</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>17,96; 91,06</t>
+          <t>18,29; 91,08</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>9,45; 22,01</t>
+          <t>9,03; 21,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>13,93; 26,91</t>
+          <t>14,02; 27,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12,68; 25,57</t>
+          <t>12,96; 26,08</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8,82; 19,6</t>
+          <t>8,84; 19,13</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,2; 51,37</t>
+          <t>6,33; 51,24</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,32; 36,1</t>
+          <t>12,45; 37,06</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,04; 31,2</t>
+          <t>10,35; 31,66</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>14,92; 27,99</t>
+          <t>14,56; 27,54</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10,12; 22,64</t>
+          <t>10,47; 22,77</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15,5; 27,12</t>
+          <t>15,5; 27,34</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13,46; 24,43</t>
+          <t>13,45; 24,57</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>12,16; 20,87</t>
+          <t>12,19; 20,4</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7,86; 21,26</t>
+          <t>8,21; 20,64</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,5; 16,64</t>
+          <t>6,45; 15,97</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9,11; 21,37</t>
+          <t>9,72; 21,73</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8,46; 17,52</t>
+          <t>8,37; 17,16</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,35; 56,92</t>
+          <t>6,37; 54,13</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,34; 76,84</t>
+          <t>10,32; 79,75</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,46; 38,1</t>
+          <t>6,69; 34,38</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6,25; 21,1</t>
+          <t>6,52; 21,0</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8,52; 21,31</t>
+          <t>9,14; 20,92</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>7,91; 17,98</t>
+          <t>7,8; 18,5</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10,5; 21,25</t>
+          <t>10,87; 21,61</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>9,15; 16,2</t>
+          <t>9,08; 16,12</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,76; 7,91</t>
+          <t>0,76; 6,92</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,18; 10,3</t>
+          <t>2,1; 10,1</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,53; 8,35</t>
+          <t>1,53; 8,47</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,25; 7,3</t>
+          <t>1,44; 7,23</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 66,26</t>
+          <t>0,0; 63,42</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0; 5,78</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,99</t>
+          <t>0,7; 6,6</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2,1; 10,17</t>
+          <t>2,14; 9,92</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,41; 8,12</t>
+          <t>1,84; 8,94</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,17; 6,52</t>
+          <t>1,05; 5,75</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>20,43; 27,33</t>
+          <t>20,28; 27,19</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>23,74; 30,34</t>
+          <t>23,65; 30,14</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>20,39; 26,94</t>
+          <t>20,09; 26,88</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14,17; 70,28</t>
+          <t>14,27; 74,84</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>31,55; 43,81</t>
+          <t>31,47; 43,64</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>31,08; 41,17</t>
+          <t>31,07; 41,53</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,9; 36,43</t>
+          <t>26,98; 36,62</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>22,19; 30,87</t>
+          <t>22,8; 31,65</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>24,84; 30,81</t>
+          <t>24,6; 30,87</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>27,37; 32,66</t>
+          <t>27,33; 32,53</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>23,61; 29,11</t>
+          <t>23,76; 29,03</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>18,35; 66,72</t>
+          <t>18,47; 65,18</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que dejo de fumar hace menos tiempo (3.374 años)</t>
+          <t>Población que dejo de fumar hace menos tiempo (3.374 años) (tasa de respuesta: 96,5%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6178; 11288</t>
+          <t>6073; 11288</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>12314; 16785</t>
+          <t>11508; 16785</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8626; 10402</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4260; 7663</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>7186; 12915</t>
+          <t>7356; 12915</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11403; 18275</t>
+          <t>10846; 18277</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8892; 16545</t>
+          <t>9445; 16537</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6984; 16689</t>
+          <t>6348; 16689</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>16144; 23261</t>
+          <t>16218; 23254</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>26190; 34170</t>
+          <t>26663; 35022</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>18191; 26950</t>
+          <t>18977; 26975</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>12730; 24351</t>
+          <t>13369; 24351</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15716; 27876</t>
+          <t>15440; 27811</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>45894; 60254</t>
+          <t>44988; 59912</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18950; 34311</t>
+          <t>18742; 33415</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3353; 14309</t>
+          <t>3030; 13891</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>31377; 48748</t>
+          <t>32784; 48978</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>41187; 60173</t>
+          <t>41929; 59906</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28593; 43312</t>
+          <t>27704; 43789</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8738; 20054</t>
+          <t>8870; 21070</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>53002; 73280</t>
+          <t>53435; 73428</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>92226; 116314</t>
+          <t>93179; 117569</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>50828; 72669</t>
+          <t>51071; 73176</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14635; 31371</t>
+          <t>15320; 31439</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>27249; 45225</t>
+          <t>27992; 45717</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>36416; 58089</t>
+          <t>37585; 58095</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>30542; 48870</t>
+          <t>29680; 49125</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7056; 21008</t>
+          <t>7367; 21020</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>8790; 23041</t>
+          <t>9555; 23139</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>24968; 45637</t>
+          <t>24920; 46248</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21373; 39818</t>
+          <t>20500; 38265</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>12147; 23244</t>
+          <t>12169; 23488</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>41326; 65963</t>
+          <t>41808; 64664</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>67704; 97128</t>
+          <t>66456; 97288</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>54058; 80963</t>
+          <t>55041; 82007</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>22821; 40371</t>
+          <t>23585; 41653</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>28666; 49767</t>
+          <t>29268; 50539</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>38294; 62665</t>
+          <t>38557; 63890</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>23363; 42394</t>
+          <t>22204; 43233</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>49580; 328495</t>
+          <t>50779; 327366</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>13742; 27768</t>
+          <t>12757; 27750</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15038; 32535</t>
+          <t>15342; 32511</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>14189; 32355</t>
+          <t>14833; 32008</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>14548; 27265</t>
+          <t>14417; 27187</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>48543; 72956</t>
+          <t>47103; 72610</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>57710; 87877</t>
+          <t>59527; 89346</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>42265; 68380</t>
+          <t>42922; 69382</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>78082; 395792</t>
+          <t>79503; 395858</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>12182; 28374</t>
+          <t>11638; 27614</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>20430; 39485</t>
+          <t>20564; 39764</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>20163; 40658</t>
+          <t>20613; 41468</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>13528; 30067</t>
+          <t>13560; 29344</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1011; 8369</t>
+          <t>1031; 8349</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6374; 18684</t>
+          <t>6445; 19182</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7540; 21300</t>
+          <t>7068; 21617</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>12764; 23952</t>
+          <t>12455; 23566</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>14700; 32872</t>
+          <t>15200; 33071</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>30755; 53826</t>
+          <t>30761; 54266</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>30584; 55529</t>
+          <t>30571; 55838</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>29048; 49868</t>
+          <t>29118; 48743</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>9416; 25480</t>
+          <t>9844; 24735</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>10969; 28093</t>
+          <t>10882; 26954</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>12714; 29834</t>
+          <t>13566; 30335</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>13037; 26997</t>
+          <t>12900; 26448</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>730; 6550</t>
+          <t>733; 6228</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1099; 8162</t>
+          <t>1096; 8472</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2916; 11746</t>
+          <t>2061; 10600</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2741; 9248</t>
+          <t>2859; 9205</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>11198; 27991</t>
+          <t>12006; 27477</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>14187; 32249</t>
+          <t>13988; 33191</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>17903; 36224</t>
+          <t>18535; 36827</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>18105; 32063</t>
+          <t>17983; 31910</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>814; 8514</t>
+          <t>823; 7444</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3081; 14573</t>
+          <t>2977; 14297</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1795; 9784</t>
+          <t>1787; 9916</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1442; 8437</t>
+          <t>1667; 8355</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 2128</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 4246</t>
+          <t>0; 4064</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 1939</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0; 962</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 6935</t>
+          <t>815; 7637</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3112; 15043</t>
+          <t>3164; 14677</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1712; 9859</t>
+          <t>2241; 10856</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1551; 8620</t>
+          <t>1384; 7600</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>125205; 167489</t>
+          <t>124287; 166633</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>196522; 251189</t>
+          <t>195806; 249507</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>141854; 187411</t>
+          <t>139744; 186942</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>119283; 591810</t>
+          <t>120136; 630142</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>78394; 108845</t>
+          <t>78185; 108434</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>121547; 161016</t>
+          <t>121524; 162416</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>102930; 139379</t>
+          <t>103228; 140116</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>73655; 102448</t>
+          <t>75678; 105035</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>213945; 265436</t>
+          <t>211891; 265948</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>333682; 398064</t>
+          <t>333130; 396541</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>254596; 313914</t>
+          <t>256191; 312961</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>215406; 783181</t>
+          <t>216793; 765163</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/Q25_A_R3-Edad-trans_dic.xlsx
+++ b/data/trans_dic/Q25_A_R3-Edad-trans_dic.xlsx
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>76,1%</t>
+          <t>78,12%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>83,62%</t>
+          <t>83,77%</t>
         </is>
       </c>
     </row>
@@ -717,12 +717,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>53,8; 100,0</t>
+          <t>48,85; 100,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>68,56; 100,0</t>
+          <t>74,78; 100,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -737,42 +737,42 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>56,96; 100,0</t>
+          <t>60,6; 100,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>56,4; 95,05</t>
+          <t>58,95; 95,23</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>51,06; 89,39</t>
+          <t>46,91; 89,54</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>38,03; 100,0</t>
+          <t>43,48; 100,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>67,01; 96,08</t>
+          <t>67,39; 96,1</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>74,04; 97,24</t>
+          <t>71,77; 94,93</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>65,66; 93,33</t>
+          <t>65,25; 93,28</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>54,9; 100,0</t>
+          <t>52,18; 100,0</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>43,22%</t>
+          <t>46,37%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>47,06%</t>
+          <t>43,09%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>45,58%</t>
+          <t>44,46%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>43,56; 78,46</t>
+          <t>46,4; 79,62</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>61,05; 81,3</t>
+          <t>60,19; 81,53</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>35,51; 63,3</t>
+          <t>36,61; 63,52</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15,84; 72,63</t>
+          <t>21,19; 74,35</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>46,03; 68,77</t>
+          <t>45,65; 69,38</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>49,71; 71,03</t>
+          <t>49,61; 72,09</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>45,6; 72,07</t>
+          <t>46,99; 72,22</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>29,04; 68,99</t>
+          <t>26,13; 62,22</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>50,1; 68,84</t>
+          <t>50,03; 69,65</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>58,96; 74,39</t>
+          <t>58,57; 74,03</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44,98; 64,45</t>
+          <t>45,01; 64,09</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>30,85; 63,3</t>
+          <t>29,28; 59,12</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>35,02%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>33,22%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>33,23; 54,27</t>
+          <t>33,07; 54,38</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>34,35; 53,1</t>
+          <t>33,66; 53,59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>34,56; 57,2</t>
+          <t>33,73; 56,14</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16,73; 47,75</t>
+          <t>17,67; 48,64</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14,38; 34,83</t>
+          <t>14,71; 35,21</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19,76; 36,68</t>
+          <t>20,0; 36,32</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,85; 38,92</t>
+          <t>21,18; 38,65</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>23,31; 44,99</t>
+          <t>24,29; 46,94</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>27,75; 42,92</t>
+          <t>27,74; 42,98</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>28,22; 41,31</t>
+          <t>29,5; 42,0</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>29,88; 44,52</t>
+          <t>29,33; 43,66</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>24,51; 43,29</t>
+          <t>24,28; 42,27</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>75,29%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>64,97%</t>
+          <t>20,52%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>23,31; 40,25</t>
+          <t>23,15; 40,16</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>22,55; 37,37</t>
+          <t>22,44; 37,43</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16,98; 33,06</t>
+          <t>17,34; 33,61</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14,58; 94,01</t>
+          <t>10,8; 26,61</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>20,56; 44,72</t>
+          <t>20,41; 45,62</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,56; 35,08</t>
+          <t>16,93; 35,98</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,6; 31,51</t>
+          <t>15,33; 32,22</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>16,68; 31,46</t>
+          <t>17,5; 32,67</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>25,11; 38,7</t>
+          <t>24,73; 38,14</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>22,58; 33,89</t>
+          <t>21,68; 33,68</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18,47; 29,86</t>
+          <t>18,31; 29,33</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>18,29; 91,08</t>
+          <t>16,4; 26,72</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,49%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>9,03; 21,42</t>
+          <t>9,53; 21,59</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>14,02; 27,1</t>
+          <t>13,63; 27,52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12,96; 26,08</t>
+          <t>12,79; 25,45</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8,84; 19,13</t>
+          <t>9,72; 19,91</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,33; 51,24</t>
+          <t>7,79; 52,19</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,45; 37,06</t>
+          <t>11,62; 35,87</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,35; 31,66</t>
+          <t>10,48; 30,34</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>14,56; 27,54</t>
+          <t>14,03; 27,08</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10,47; 22,77</t>
+          <t>10,76; 22,64</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15,5; 27,34</t>
+          <t>15,55; 27,72</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13,45; 24,57</t>
+          <t>13,74; 24,93</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>12,19; 20,4</t>
+          <t>12,54; 20,75</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,61%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8,21; 20,64</t>
+          <t>8,03; 20,63</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,45; 15,97</t>
+          <t>6,46; 15,91</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9,72; 21,73</t>
+          <t>9,41; 21,38</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8,37; 17,16</t>
+          <t>8,54; 17,59</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,37; 54,13</t>
+          <t>6,59; 57,11</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,32; 79,75</t>
+          <t>11,05; 78,58</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,69; 34,38</t>
+          <t>6,83; 36,85</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6,52; 21,0</t>
+          <t>7,17; 22,26</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9,14; 20,92</t>
+          <t>8,76; 20,86</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>7,8; 18,5</t>
+          <t>8,2; 18,48</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10,87; 21,61</t>
+          <t>10,82; 21,94</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>9,08; 16,12</t>
+          <t>9,34; 16,62</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -1557,22 +1557,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,76; 6,92</t>
+          <t>0,77; 7,11</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,1; 10,1</t>
+          <t>2,13; 9,8</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,53; 8,47</t>
+          <t>1,46; 9,22</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,44; 7,23</t>
+          <t>1,28; 7,33</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 63,42</t>
+          <t>0,0; 65,26</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1597,22 +1597,22 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,7; 6,6</t>
+          <t>0,7; 6,54</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2,14; 9,92</t>
+          <t>2,76; 10,53</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,84; 8,94</t>
+          <t>1,42; 8,8</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,05; 5,75</t>
+          <t>1,14; 6,35</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>39,92%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>19,56%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>20,28; 27,19</t>
+          <t>20,69; 27,44</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>23,65; 30,14</t>
+          <t>23,85; 30,13</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>20,09; 26,88</t>
+          <t>20,46; 26,92</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14,27; 74,84</t>
+          <t>12,74; 18,78</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>31,47; 43,64</t>
+          <t>31,96; 44,19</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>31,07; 41,53</t>
+          <t>31,47; 41,19</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,98; 36,62</t>
+          <t>26,9; 36,18</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>22,8; 31,65</t>
+          <t>23,0; 31,54</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>24,6; 30,87</t>
+          <t>24,84; 30,98</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>27,33; 32,53</t>
+          <t>27,45; 33,11</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>23,76; 29,03</t>
+          <t>23,52; 29,11</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>18,47; 65,18</t>
+          <t>17,13; 22,23</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7663</t>
+          <t>6465</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>12700</t>
+          <t>14522</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>20362</t>
+          <t>20987</t>
         </is>
       </c>
     </row>
@@ -2068,12 +2068,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6073; 11288</t>
+          <t>5515; 11288</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>11508; 16785</t>
+          <t>12552; 16785</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -2088,42 +2088,42 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>7356; 12915</t>
+          <t>7827; 12915</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10846; 18277</t>
+          <t>11336; 18311</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9445; 16537</t>
+          <t>8678; 16565</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6348; 16689</t>
+          <t>8083; 18589</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>16218; 23254</t>
+          <t>16310; 23259</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>26663; 35022</t>
+          <t>25846; 34189</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>18977; 26975</t>
+          <t>18859; 26961</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>13369; 24351</t>
+          <t>13074; 25054</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8266</t>
+          <t>11359</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>14373</t>
+          <t>14679</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>22639</t>
+          <t>26038</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15440; 27811</t>
+          <t>16449; 28222</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>44988; 59912</t>
+          <t>44352; 60085</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18742; 33415</t>
+          <t>19323; 33531</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3030; 13891</t>
+          <t>5191; 18214</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>32784; 48978</t>
+          <t>32510; 49413</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>41929; 59906</t>
+          <t>41840; 60806</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>27704; 43789</t>
+          <t>28549; 43878</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8870; 21070</t>
+          <t>8901; 21196</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>53435; 73428</t>
+          <t>53362; 74295</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>93179; 117569</t>
+          <t>92567; 116989</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>51071; 73176</t>
+          <t>51104; 72767</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>15320; 31439</t>
+          <t>17146; 34624</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13602</t>
+          <t>15026</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>17373</t>
+          <t>19786</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>30974</t>
+          <t>34813</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>27992; 45717</t>
+          <t>27856; 45802</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>37585; 58095</t>
+          <t>36827; 58629</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>29680; 49125</t>
+          <t>28973; 48217</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7367; 21020</t>
+          <t>8532; 23487</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>9555; 23139</t>
+          <t>9776; 23389</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>24920; 46248</t>
+          <t>25213; 45794</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20500; 38265</t>
+          <t>20829; 38001</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>12169; 23488</t>
+          <t>13724; 26520</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>41808; 64664</t>
+          <t>41795; 64753</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>66456; 97288</t>
+          <t>69477; 98899</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>55041; 82007</t>
+          <t>54032; 80435</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>23585; 41653</t>
+          <t>25439; 44290</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>262162</t>
+          <t>19884</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>20201</t>
+          <t>22442</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>282364</t>
+          <t>42326</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>29268; 50539</t>
+          <t>29063; 50420</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>38557; 63890</t>
+          <t>38365; 63991</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>22204; 43233</t>
+          <t>22675; 43953</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>50779; 327366</t>
+          <t>12376; 30485</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12757; 27750</t>
+          <t>12667; 28311</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15342; 32511</t>
+          <t>15692; 33343</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>14833; 32008</t>
+          <t>15575; 32723</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>14417; 27187</t>
+          <t>16052; 29965</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>47103; 72610</t>
+          <t>46393; 71553</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>59527; 89346</t>
+          <t>57162; 88785</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>42922; 69382</t>
+          <t>42548; 68147</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>79503; 395858</t>
+          <t>33836; 55114</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21250</t>
+          <t>23051</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>17458</t>
+          <t>19061</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>38708</t>
+          <t>42112</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>11638; 27614</t>
+          <t>12286; 27842</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>20564; 39764</t>
+          <t>19997; 40370</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>20613; 41468</t>
+          <t>20342; 40458</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>13560; 29344</t>
+          <t>15726; 32212</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1031; 8349</t>
+          <t>1270; 8503</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6445; 19182</t>
+          <t>6014; 18566</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7068; 21617</t>
+          <t>7152; 20711</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>12455; 23566</t>
+          <t>13132; 25351</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>15200; 33071</t>
+          <t>15628; 32872</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>30761; 54266</t>
+          <t>30866; 55010</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>30571; 55838</t>
+          <t>31225; 56667</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>29118; 48743</t>
+          <t>32031; 52987</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>19132</t>
+          <t>21086</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>5460</t>
+          <t>6282</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>24592</t>
+          <t>27367</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>9844; 24735</t>
+          <t>9626; 24723</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>10882; 26954</t>
+          <t>10910; 26853</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>13566; 30335</t>
+          <t>13136; 29850</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>12900; 26448</t>
+          <t>14523; 29929</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>733; 6228</t>
+          <t>758; 6571</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1096; 8472</t>
+          <t>1174; 8347</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2061; 10600</t>
+          <t>2105; 11360</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2859; 9205</t>
+          <t>3364; 10436</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>12006; 27477</t>
+          <t>11512; 27402</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>13988; 33191</t>
+          <t>14718; 33160</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>18535; 36827</t>
+          <t>18443; 37403</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>17983; 31910</t>
+          <t>20259; 36075</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4041</t>
+          <t>4542</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>4041</t>
+          <t>4542</t>
         </is>
       </c>
     </row>
@@ -3316,22 +3316,22 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>823; 7444</t>
+          <t>825; 7657</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2977; 14297</t>
+          <t>3014; 13873</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1787; 9916</t>
+          <t>1707; 10803</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1667; 8355</t>
+          <t>1635; 9341</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 4064</t>
+          <t>0; 4182</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -3356,22 +3356,22 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>815; 7637</t>
+          <t>810; 7561</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3164; 14677</t>
+          <t>4076; 15569</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2241; 10856</t>
+          <t>1721; 10687</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1384; 7600</t>
+          <t>1663; 9271</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>336115</t>
+          <t>101413</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>87565</t>
+          <t>96772</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>423679</t>
+          <t>198185</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>124287; 166633</t>
+          <t>126793; 168183</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>195806; 249507</t>
+          <t>197477; 249396</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>139744; 186942</t>
+          <t>142331; 187264</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>120136; 630142</t>
+          <t>83236; 122653</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>78185; 108434</t>
+          <t>79418; 109802</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>121524; 162416</t>
+          <t>123096; 161109</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>103228; 140116</t>
+          <t>102934; 138426</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>75678; 105035</t>
+          <t>82780; 113518</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>211891; 265948</t>
+          <t>213966; 266848</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>333130; 396541</t>
+          <t>334545; 403641</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>256191; 312961</t>
+          <t>253555; 313815</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>216793; 765163</t>
+          <t>173504; 225223</t>
         </is>
       </c>
     </row>
